--- a/TFE_PRONOSTICO/DATOS_LIGA_COLOMBIANA.xlsx
+++ b/TFE_PRONOSTICO/DATOS_LIGA_COLOMBIANA.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="948" documentId="8_{BD6864F7-2D08-4823-8130-8AEB370B13DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB5A507E-6F65-444A-BD34-132AC4831673}"/>
+  <xr:revisionPtr revIDLastSave="979" documentId="8_{BD6864F7-2D08-4823-8130-8AEB370B13DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F1A26BE-ECCF-4753-B6E3-28ADC8585D6F}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="261" r:id="rId4"/>
+    <pivotCache cacheId="1306" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -665,7 +665,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -869,47 +869,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -929,9 +890,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -27455,7 +27454,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F97A265-E442-4D37-A950-2A2116028FDB}" name="Tabla dinámica1" cacheId="261" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F97A265-E442-4D37-A950-2A2116028FDB}" name="Tabla dinámica1" cacheId="1306" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
@@ -30076,7 +30075,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
         <v>11</v>
@@ -31181,7 +31180,7 @@
         <v>23</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -33353,7 +33352,7 @@
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F188" t="s">
         <v>13</v>
@@ -34223,7 +34222,7 @@
         <v>4</v>
       </c>
       <c r="E218" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F218" t="s">
         <v>23</v>
@@ -35328,7 +35327,7 @@
         <v>24</v>
       </c>
       <c r="F256" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G256">
         <v>1</v>
@@ -38129,7 +38128,7 @@
         <v>17</v>
       </c>
       <c r="E352" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F352" t="s">
         <v>26</v>
@@ -40739,7 +40738,7 @@
         <v>3</v>
       </c>
       <c r="E439" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F439" t="s">
         <v>24</v>
@@ -43229,7 +43228,7 @@
         <v>11</v>
       </c>
       <c r="E522" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F522" t="s">
         <v>13</v>
@@ -48509,7 +48508,7 @@
         <v>6</v>
       </c>
       <c r="E698" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F698" t="s">
         <v>31</v>
@@ -77162,7 +77161,7 @@
         <v>20</v>
       </c>
       <c r="F1653" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G1653">
         <v>0</v>
@@ -93400,7 +93399,7 @@
       <c r="H2197">
         <v>2</v>
       </c>
-      <c r="I2197" s="91" t="s">
+      <c r="I2197" t="s">
         <v>30</v>
       </c>
     </row>
@@ -93429,7 +93428,7 @@
       <c r="H2198">
         <v>0</v>
       </c>
-      <c r="I2198" s="91" t="s">
+      <c r="I2198" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93458,7 +93457,7 @@
       <c r="H2199">
         <v>0</v>
       </c>
-      <c r="I2199" s="91" t="s">
+      <c r="I2199" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93487,7 +93486,7 @@
       <c r="H2200">
         <v>0</v>
       </c>
-      <c r="I2200" s="91" t="s">
+      <c r="I2200" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93516,7 +93515,7 @@
       <c r="H2201">
         <v>1</v>
       </c>
-      <c r="I2201" s="91" t="s">
+      <c r="I2201" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93545,7 +93544,7 @@
       <c r="H2202">
         <v>0</v>
       </c>
-      <c r="I2202" s="91" t="s">
+      <c r="I2202" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93574,7 +93573,7 @@
       <c r="H2203">
         <v>0</v>
       </c>
-      <c r="I2203" s="91" t="s">
+      <c r="I2203" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93603,7 +93602,7 @@
       <c r="H2204">
         <v>2</v>
       </c>
-      <c r="I2204" s="91" t="s">
+      <c r="I2204" t="s">
         <v>30</v>
       </c>
     </row>
@@ -93632,7 +93631,7 @@
       <c r="H2205">
         <v>1</v>
       </c>
-      <c r="I2205" s="91" t="s">
+      <c r="I2205" t="s">
         <v>17</v>
       </c>
     </row>
@@ -93661,7 +93660,7 @@
       <c r="H2206">
         <v>2</v>
       </c>
-      <c r="I2206" s="91" t="s">
+      <c r="I2206" t="s">
         <v>30</v>
       </c>
     </row>
@@ -93690,7 +93689,7 @@
       <c r="H2207">
         <v>1</v>
       </c>
-      <c r="I2207" s="91" t="s">
+      <c r="I2207" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93719,7 +93718,7 @@
       <c r="H2208">
         <v>0</v>
       </c>
-      <c r="I2208" s="91" t="s">
+      <c r="I2208" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93748,7 +93747,7 @@
       <c r="H2209">
         <v>0</v>
       </c>
-      <c r="I2209" s="91" t="s">
+      <c r="I2209" t="s">
         <v>17</v>
       </c>
     </row>
@@ -93777,7 +93776,7 @@
       <c r="H2210">
         <v>1</v>
       </c>
-      <c r="I2210" s="91" t="s">
+      <c r="I2210" t="s">
         <v>17</v>
       </c>
     </row>
@@ -93806,7 +93805,7 @@
       <c r="H2211">
         <v>1</v>
       </c>
-      <c r="I2211" s="91" t="s">
+      <c r="I2211" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93835,7 +93834,7 @@
       <c r="H2212">
         <v>1</v>
       </c>
-      <c r="I2212" s="91" t="s">
+      <c r="I2212" t="s">
         <v>30</v>
       </c>
     </row>
@@ -93864,7 +93863,7 @@
       <c r="H2213">
         <v>2</v>
       </c>
-      <c r="I2213" s="91" t="s">
+      <c r="I2213" t="s">
         <v>30</v>
       </c>
     </row>
@@ -93893,7 +93892,7 @@
       <c r="H2214">
         <v>2</v>
       </c>
-      <c r="I2214" s="91" t="s">
+      <c r="I2214" t="s">
         <v>30</v>
       </c>
     </row>
@@ -93922,7 +93921,7 @@
       <c r="H2215">
         <v>1</v>
       </c>
-      <c r="I2215" s="91" t="s">
+      <c r="I2215" t="s">
         <v>17</v>
       </c>
     </row>
@@ -93951,7 +93950,7 @@
       <c r="H2216">
         <v>1</v>
       </c>
-      <c r="I2216" s="91" t="s">
+      <c r="I2216" t="s">
         <v>12</v>
       </c>
     </row>
@@ -93980,7 +93979,7 @@
       <c r="H2217">
         <v>2</v>
       </c>
-      <c r="I2217" s="91" t="s">
+      <c r="I2217" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94009,7 +94008,7 @@
       <c r="H2218">
         <v>1</v>
       </c>
-      <c r="I2218" s="91" t="s">
+      <c r="I2218" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94038,7 +94037,7 @@
       <c r="H2219">
         <v>2</v>
       </c>
-      <c r="I2219" s="91" t="s">
+      <c r="I2219" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94067,7 +94066,7 @@
       <c r="H2220">
         <v>1</v>
       </c>
-      <c r="I2220" s="91" t="s">
+      <c r="I2220" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94096,7 +94095,7 @@
       <c r="H2221">
         <v>2</v>
       </c>
-      <c r="I2221" s="91" t="s">
+      <c r="I2221" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94125,7 +94124,7 @@
       <c r="H2222">
         <v>1</v>
       </c>
-      <c r="I2222" s="91" t="s">
+      <c r="I2222" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94154,7 +94153,7 @@
       <c r="H2223">
         <v>1</v>
       </c>
-      <c r="I2223" s="91" t="s">
+      <c r="I2223" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94183,7 +94182,7 @@
       <c r="H2224">
         <v>3</v>
       </c>
-      <c r="I2224" s="91" t="s">
+      <c r="I2224" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94212,7 +94211,7 @@
       <c r="H2225">
         <v>1</v>
       </c>
-      <c r="I2225" s="91" t="s">
+      <c r="I2225" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94241,7 +94240,7 @@
       <c r="H2226">
         <v>4</v>
       </c>
-      <c r="I2226" s="91" t="s">
+      <c r="I2226" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94270,7 +94269,7 @@
       <c r="H2227">
         <v>1</v>
       </c>
-      <c r="I2227" s="91" t="s">
+      <c r="I2227" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94299,7 +94298,7 @@
       <c r="H2228">
         <v>1</v>
       </c>
-      <c r="I2228" s="91" t="s">
+      <c r="I2228" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94328,7 +94327,7 @@
       <c r="H2229">
         <v>0</v>
       </c>
-      <c r="I2229" s="91" t="s">
+      <c r="I2229" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94357,7 +94356,7 @@
       <c r="H2230">
         <v>0</v>
       </c>
-      <c r="I2230" s="91" t="s">
+      <c r="I2230" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94386,7 +94385,7 @@
       <c r="H2231">
         <v>1</v>
       </c>
-      <c r="I2231" s="91" t="s">
+      <c r="I2231" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94415,7 +94414,7 @@
       <c r="H2232">
         <v>0</v>
       </c>
-      <c r="I2232" s="91" t="s">
+      <c r="I2232" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94444,7 +94443,7 @@
       <c r="H2233">
         <v>1</v>
       </c>
-      <c r="I2233" s="91" t="s">
+      <c r="I2233" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94473,7 +94472,7 @@
       <c r="H2234">
         <v>0</v>
       </c>
-      <c r="I2234" s="91" t="s">
+      <c r="I2234" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94502,7 +94501,7 @@
       <c r="H2235">
         <v>3</v>
       </c>
-      <c r="I2235" s="91" t="s">
+      <c r="I2235" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94531,7 +94530,7 @@
       <c r="H2236">
         <v>1</v>
       </c>
-      <c r="I2236" s="91" t="s">
+      <c r="I2236" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94560,7 +94559,7 @@
       <c r="H2237">
         <v>0</v>
       </c>
-      <c r="I2237" s="91" t="s">
+      <c r="I2237" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94589,7 +94588,7 @@
       <c r="H2238">
         <v>2</v>
       </c>
-      <c r="I2238" s="91" t="s">
+      <c r="I2238" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94618,7 +94617,7 @@
       <c r="H2239">
         <v>2</v>
       </c>
-      <c r="I2239" s="91" t="s">
+      <c r="I2239" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94647,7 +94646,7 @@
       <c r="H2240">
         <v>1</v>
       </c>
-      <c r="I2240" s="91" t="s">
+      <c r="I2240" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94676,7 +94675,7 @@
       <c r="H2241">
         <v>0</v>
       </c>
-      <c r="I2241" s="91" t="s">
+      <c r="I2241" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94705,7 +94704,7 @@
       <c r="H2242">
         <v>1</v>
       </c>
-      <c r="I2242" s="91" t="s">
+      <c r="I2242" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94734,7 +94733,7 @@
       <c r="H2243">
         <v>0</v>
       </c>
-      <c r="I2243" s="91" t="s">
+      <c r="I2243" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94763,7 +94762,7 @@
       <c r="H2244">
         <v>0</v>
       </c>
-      <c r="I2244" s="91" t="s">
+      <c r="I2244" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94792,7 +94791,7 @@
       <c r="H2245">
         <v>2</v>
       </c>
-      <c r="I2245" s="91" t="s">
+      <c r="I2245" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94821,7 +94820,7 @@
       <c r="H2246">
         <v>2</v>
       </c>
-      <c r="I2246" s="91" t="s">
+      <c r="I2246" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94850,7 +94849,7 @@
       <c r="H2247">
         <v>3</v>
       </c>
-      <c r="I2247" s="91" t="s">
+      <c r="I2247" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94879,7 +94878,7 @@
       <c r="H2248">
         <v>1</v>
       </c>
-      <c r="I2248" s="91" t="s">
+      <c r="I2248" t="s">
         <v>30</v>
       </c>
     </row>
@@ -94908,7 +94907,7 @@
       <c r="H2249">
         <v>0</v>
       </c>
-      <c r="I2249" s="91" t="s">
+      <c r="I2249" t="s">
         <v>17</v>
       </c>
     </row>
@@ -94937,7 +94936,7 @@
       <c r="H2250">
         <v>0</v>
       </c>
-      <c r="I2250" s="91" t="s">
+      <c r="I2250" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94966,7 +94965,7 @@
       <c r="H2251">
         <v>2</v>
       </c>
-      <c r="I2251" s="91" t="s">
+      <c r="I2251" t="s">
         <v>12</v>
       </c>
     </row>
@@ -94995,7 +94994,7 @@
       <c r="H2252">
         <v>0</v>
       </c>
-      <c r="I2252" s="91" t="s">
+      <c r="I2252" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95024,7 +95023,7 @@
       <c r="H2253">
         <v>1</v>
       </c>
-      <c r="I2253" s="91" t="s">
+      <c r="I2253" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95053,7 +95052,7 @@
       <c r="H2254">
         <v>1</v>
       </c>
-      <c r="I2254" s="91" t="s">
+      <c r="I2254" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95082,7 +95081,7 @@
       <c r="H2255">
         <v>0</v>
       </c>
-      <c r="I2255" s="91" t="s">
+      <c r="I2255" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95111,7 +95110,7 @@
       <c r="H2256">
         <v>3</v>
       </c>
-      <c r="I2256" s="91" t="s">
+      <c r="I2256" t="s">
         <v>30</v>
       </c>
     </row>
@@ -95140,7 +95139,7 @@
       <c r="H2257">
         <v>1</v>
       </c>
-      <c r="I2257" s="91" t="s">
+      <c r="I2257" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95169,7 +95168,7 @@
       <c r="H2258">
         <v>1</v>
       </c>
-      <c r="I2258" s="91" t="s">
+      <c r="I2258" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95198,7 +95197,7 @@
       <c r="H2259">
         <v>1</v>
       </c>
-      <c r="I2259" s="91" t="s">
+      <c r="I2259" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95227,7 +95226,7 @@
       <c r="H2260">
         <v>1</v>
       </c>
-      <c r="I2260" s="91" t="s">
+      <c r="I2260" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95256,7 +95255,7 @@
       <c r="H2261">
         <v>0</v>
       </c>
-      <c r="I2261" s="91" t="s">
+      <c r="I2261" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95285,7 +95284,7 @@
       <c r="H2262">
         <v>1</v>
       </c>
-      <c r="I2262" s="91" t="s">
+      <c r="I2262" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95314,7 +95313,7 @@
       <c r="H2263">
         <v>1</v>
       </c>
-      <c r="I2263" s="91" t="s">
+      <c r="I2263" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95343,7 +95342,7 @@
       <c r="H2264">
         <v>1</v>
       </c>
-      <c r="I2264" s="91" t="s">
+      <c r="I2264" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95372,7 +95371,7 @@
       <c r="H2265">
         <v>1</v>
       </c>
-      <c r="I2265" s="91" t="s">
+      <c r="I2265" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95401,7 +95400,7 @@
       <c r="H2266">
         <v>1</v>
       </c>
-      <c r="I2266" s="91" t="s">
+      <c r="I2266" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95430,7 +95429,7 @@
       <c r="H2267">
         <v>2</v>
       </c>
-      <c r="I2267" s="91" t="s">
+      <c r="I2267" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95459,7 +95458,7 @@
       <c r="H2268">
         <v>2</v>
       </c>
-      <c r="I2268" s="91" t="s">
+      <c r="I2268" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95488,7 +95487,7 @@
       <c r="H2269">
         <v>2</v>
       </c>
-      <c r="I2269" s="91" t="s">
+      <c r="I2269" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95517,7 +95516,7 @@
       <c r="H2270">
         <v>0</v>
       </c>
-      <c r="I2270" s="91" t="s">
+      <c r="I2270" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95546,7 +95545,7 @@
       <c r="H2271">
         <v>0</v>
       </c>
-      <c r="I2271" s="91" t="s">
+      <c r="I2271" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95575,7 +95574,7 @@
       <c r="H2272">
         <v>2</v>
       </c>
-      <c r="I2272" s="91" t="s">
+      <c r="I2272" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95604,7 +95603,7 @@
       <c r="H2273">
         <v>1</v>
       </c>
-      <c r="I2273" s="91" t="s">
+      <c r="I2273" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95633,7 +95632,7 @@
       <c r="H2274">
         <v>1</v>
       </c>
-      <c r="I2274" s="91" t="s">
+      <c r="I2274" t="s">
         <v>30</v>
       </c>
     </row>
@@ -95662,7 +95661,7 @@
       <c r="H2275">
         <v>0</v>
       </c>
-      <c r="I2275" s="91" t="s">
+      <c r="I2275" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95691,7 +95690,7 @@
       <c r="H2276">
         <v>2</v>
       </c>
-      <c r="I2276" s="91" t="s">
+      <c r="I2276" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95720,7 +95719,7 @@
       <c r="H2277">
         <v>1</v>
       </c>
-      <c r="I2277" s="91" t="s">
+      <c r="I2277" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95749,7 +95748,7 @@
       <c r="H2278">
         <v>1</v>
       </c>
-      <c r="I2278" s="91" t="s">
+      <c r="I2278" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95778,7 +95777,7 @@
       <c r="H2279">
         <v>0</v>
       </c>
-      <c r="I2279" s="91" t="s">
+      <c r="I2279" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95807,7 +95806,7 @@
       <c r="H2280">
         <v>3</v>
       </c>
-      <c r="I2280" s="91" t="s">
+      <c r="I2280" t="s">
         <v>30</v>
       </c>
     </row>
@@ -95836,7 +95835,7 @@
       <c r="H2281">
         <v>2</v>
       </c>
-      <c r="I2281" s="91" t="s">
+      <c r="I2281" t="s">
         <v>30</v>
       </c>
     </row>
@@ -95865,7 +95864,7 @@
       <c r="H2282">
         <v>2</v>
       </c>
-      <c r="I2282" s="91" t="s">
+      <c r="I2282" t="s">
         <v>30</v>
       </c>
     </row>
@@ -95894,7 +95893,7 @@
       <c r="H2283">
         <v>2</v>
       </c>
-      <c r="I2283" s="91" t="s">
+      <c r="I2283" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95923,7 +95922,7 @@
       <c r="H2284">
         <v>0</v>
       </c>
-      <c r="I2284" s="91" t="s">
+      <c r="I2284" t="s">
         <v>17</v>
       </c>
     </row>
@@ -95952,7 +95951,7 @@
       <c r="H2285">
         <v>0</v>
       </c>
-      <c r="I2285" s="91" t="s">
+      <c r="I2285" t="s">
         <v>12</v>
       </c>
     </row>
@@ -95981,7 +95980,7 @@
       <c r="H2286">
         <v>1</v>
       </c>
-      <c r="I2286" s="91" t="s">
+      <c r="I2286" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96010,7 +96009,7 @@
       <c r="H2287">
         <v>1</v>
       </c>
-      <c r="I2287" s="91" t="s">
+      <c r="I2287" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96039,7 +96038,7 @@
       <c r="H2288">
         <v>1</v>
       </c>
-      <c r="I2288" s="91" t="s">
+      <c r="I2288" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96068,7 +96067,7 @@
       <c r="H2289">
         <v>1</v>
       </c>
-      <c r="I2289" s="91" t="s">
+      <c r="I2289" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96097,7 +96096,7 @@
       <c r="H2290">
         <v>2</v>
       </c>
-      <c r="I2290" s="91" t="s">
+      <c r="I2290" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96126,7 +96125,7 @@
       <c r="H2291">
         <v>2</v>
       </c>
-      <c r="I2291" s="91" t="s">
+      <c r="I2291" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96155,7 +96154,7 @@
       <c r="H2292">
         <v>0</v>
       </c>
-      <c r="I2292" s="91" t="s">
+      <c r="I2292" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96184,7 +96183,7 @@
       <c r="H2293">
         <v>0</v>
       </c>
-      <c r="I2293" s="91" t="s">
+      <c r="I2293" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96213,7 +96212,7 @@
       <c r="H2294">
         <v>0</v>
       </c>
-      <c r="I2294" s="91" t="s">
+      <c r="I2294" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96242,7 +96241,7 @@
       <c r="H2295">
         <v>2</v>
       </c>
-      <c r="I2295" s="91" t="s">
+      <c r="I2295" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96271,7 +96270,7 @@
       <c r="H2296">
         <v>0</v>
       </c>
-      <c r="I2296" s="91" t="s">
+      <c r="I2296" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96300,7 +96299,7 @@
       <c r="H2297">
         <v>2</v>
       </c>
-      <c r="I2297" s="91" t="s">
+      <c r="I2297" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96329,7 +96328,7 @@
       <c r="H2298">
         <v>0</v>
       </c>
-      <c r="I2298" s="91" t="s">
+      <c r="I2298" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96358,7 +96357,7 @@
       <c r="H2299">
         <v>0</v>
       </c>
-      <c r="I2299" s="91" t="s">
+      <c r="I2299" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96387,7 +96386,7 @@
       <c r="H2300">
         <v>2</v>
       </c>
-      <c r="I2300" s="91" t="s">
+      <c r="I2300" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96416,7 +96415,7 @@
       <c r="H2301">
         <v>1</v>
       </c>
-      <c r="I2301" s="91" t="s">
+      <c r="I2301" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96445,7 +96444,7 @@
       <c r="H2302">
         <v>1</v>
       </c>
-      <c r="I2302" s="91" t="s">
+      <c r="I2302" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96474,7 +96473,7 @@
       <c r="H2303">
         <v>1</v>
       </c>
-      <c r="I2303" s="91" t="s">
+      <c r="I2303" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96503,7 +96502,7 @@
       <c r="H2304">
         <v>1</v>
       </c>
-      <c r="I2304" s="91" t="s">
+      <c r="I2304" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96532,7 +96531,7 @@
       <c r="H2305">
         <v>2</v>
       </c>
-      <c r="I2305" s="91" t="s">
+      <c r="I2305" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96561,7 +96560,7 @@
       <c r="H2306">
         <v>1</v>
       </c>
-      <c r="I2306" s="91" t="s">
+      <c r="I2306" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96590,7 +96589,7 @@
       <c r="H2307">
         <v>2</v>
       </c>
-      <c r="I2307" s="91" t="s">
+      <c r="I2307" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96619,7 +96618,7 @@
       <c r="H2308">
         <v>0</v>
       </c>
-      <c r="I2308" s="91" t="s">
+      <c r="I2308" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96648,7 +96647,7 @@
       <c r="H2309">
         <v>0</v>
       </c>
-      <c r="I2309" s="91" t="s">
+      <c r="I2309" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96677,7 +96676,7 @@
       <c r="H2310">
         <v>2</v>
       </c>
-      <c r="I2310" s="91" t="s">
+      <c r="I2310" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96706,7 +96705,7 @@
       <c r="H2311">
         <v>1</v>
       </c>
-      <c r="I2311" s="91" t="s">
+      <c r="I2311" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96735,7 +96734,7 @@
       <c r="H2312">
         <v>1</v>
       </c>
-      <c r="I2312" s="91" t="s">
+      <c r="I2312" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96764,7 +96763,7 @@
       <c r="H2313">
         <v>0</v>
       </c>
-      <c r="I2313" s="91" t="s">
+      <c r="I2313" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96793,7 +96792,7 @@
       <c r="H2314">
         <v>0</v>
       </c>
-      <c r="I2314" s="91" t="s">
+      <c r="I2314" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96822,7 +96821,7 @@
       <c r="H2315">
         <v>0</v>
       </c>
-      <c r="I2315" s="91" t="s">
+      <c r="I2315" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96851,7 +96850,7 @@
       <c r="H2316">
         <v>1</v>
       </c>
-      <c r="I2316" s="91" t="s">
+      <c r="I2316" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96880,7 +96879,7 @@
       <c r="H2317">
         <v>4</v>
       </c>
-      <c r="I2317" s="91" t="s">
+      <c r="I2317" t="s">
         <v>30</v>
       </c>
     </row>
@@ -96909,7 +96908,7 @@
       <c r="H2318">
         <v>0</v>
       </c>
-      <c r="I2318" s="91" t="s">
+      <c r="I2318" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96938,7 +96937,7 @@
       <c r="H2319">
         <v>0</v>
       </c>
-      <c r="I2319" s="91" t="s">
+      <c r="I2319" t="s">
         <v>12</v>
       </c>
     </row>
@@ -96967,7 +96966,7 @@
       <c r="H2320">
         <v>1</v>
       </c>
-      <c r="I2320" s="91" t="s">
+      <c r="I2320" t="s">
         <v>17</v>
       </c>
     </row>
@@ -96996,7 +96995,7 @@
       <c r="H2321">
         <v>1</v>
       </c>
-      <c r="I2321" s="91" t="s">
+      <c r="I2321" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97025,7 +97024,7 @@
       <c r="H2322">
         <v>1</v>
       </c>
-      <c r="I2322" s="91" t="s">
+      <c r="I2322" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97054,7 +97053,7 @@
       <c r="H2323">
         <v>2</v>
       </c>
-      <c r="I2323" s="91" t="s">
+      <c r="I2323" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97083,7 +97082,7 @@
       <c r="H2324">
         <v>0</v>
       </c>
-      <c r="I2324" s="91" t="s">
+      <c r="I2324" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97112,7 +97111,7 @@
       <c r="H2325">
         <v>2</v>
       </c>
-      <c r="I2325" s="91" t="s">
+      <c r="I2325" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97141,7 +97140,7 @@
       <c r="H2326">
         <v>0</v>
       </c>
-      <c r="I2326" s="91" t="s">
+      <c r="I2326" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97170,7 +97169,7 @@
       <c r="H2327">
         <v>0</v>
       </c>
-      <c r="I2327" s="91" t="s">
+      <c r="I2327" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97199,7 +97198,7 @@
       <c r="H2328">
         <v>2</v>
       </c>
-      <c r="I2328" s="91" t="s">
+      <c r="I2328" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97228,7 +97227,7 @@
       <c r="H2329">
         <v>0</v>
       </c>
-      <c r="I2329" s="91" t="s">
+      <c r="I2329" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97257,7 +97256,7 @@
       <c r="H2330">
         <v>1</v>
       </c>
-      <c r="I2330" s="91" t="s">
+      <c r="I2330" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97286,7 +97285,7 @@
       <c r="H2331">
         <v>0</v>
       </c>
-      <c r="I2331" s="91" t="s">
+      <c r="I2331" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97315,7 +97314,7 @@
       <c r="H2332">
         <v>1</v>
       </c>
-      <c r="I2332" s="91" t="s">
+      <c r="I2332" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97344,7 +97343,7 @@
       <c r="H2333">
         <v>2</v>
       </c>
-      <c r="I2333" s="91" t="s">
+      <c r="I2333" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97373,7 +97372,7 @@
       <c r="H2334">
         <v>1</v>
       </c>
-      <c r="I2334" s="91" t="s">
+      <c r="I2334" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97394,7 +97393,7 @@
         <v>14</v>
       </c>
       <c r="F2335" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2335">
         <v>2</v>
@@ -97402,7 +97401,7 @@
       <c r="H2335">
         <v>1</v>
       </c>
-      <c r="I2335" s="91" t="s">
+      <c r="I2335" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97431,7 +97430,7 @@
       <c r="H2336">
         <v>2</v>
       </c>
-      <c r="I2336" s="91" t="s">
+      <c r="I2336" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97460,7 +97459,7 @@
       <c r="H2337">
         <v>1</v>
       </c>
-      <c r="I2337" s="91" t="s">
+      <c r="I2337" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97489,7 +97488,7 @@
       <c r="H2338">
         <v>0</v>
       </c>
-      <c r="I2338" s="91" t="s">
+      <c r="I2338" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97518,7 +97517,7 @@
       <c r="H2339">
         <v>1</v>
       </c>
-      <c r="I2339" s="91" t="s">
+      <c r="I2339" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97547,7 +97546,7 @@
       <c r="H2340">
         <v>0</v>
       </c>
-      <c r="I2340" s="91" t="s">
+      <c r="I2340" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97576,7 +97575,7 @@
       <c r="H2341">
         <v>0</v>
       </c>
-      <c r="I2341" s="91" t="s">
+      <c r="I2341" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97605,7 +97604,7 @@
       <c r="H2342">
         <v>0</v>
       </c>
-      <c r="I2342" s="91" t="s">
+      <c r="I2342" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97634,7 +97633,7 @@
       <c r="H2343">
         <v>0</v>
       </c>
-      <c r="I2343" s="91" t="s">
+      <c r="I2343" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97663,7 +97662,7 @@
       <c r="H2344">
         <v>1</v>
       </c>
-      <c r="I2344" s="91" t="s">
+      <c r="I2344" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97692,7 +97691,7 @@
       <c r="H2345">
         <v>1</v>
       </c>
-      <c r="I2345" s="91" t="s">
+      <c r="I2345" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97721,7 +97720,7 @@
       <c r="H2346">
         <v>2</v>
       </c>
-      <c r="I2346" s="91" t="s">
+      <c r="I2346" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97750,7 +97749,7 @@
       <c r="H2347">
         <v>1</v>
       </c>
-      <c r="I2347" s="91" t="s">
+      <c r="I2347" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97779,7 +97778,7 @@
       <c r="H2348">
         <v>0</v>
       </c>
-      <c r="I2348" s="91" t="s">
+      <c r="I2348" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97800,7 +97799,7 @@
         <v>41</v>
       </c>
       <c r="F2349" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G2349">
         <v>2</v>
@@ -97808,7 +97807,7 @@
       <c r="H2349">
         <v>0</v>
       </c>
-      <c r="I2349" s="91" t="s">
+      <c r="I2349" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97837,7 +97836,7 @@
       <c r="H2350">
         <v>0</v>
       </c>
-      <c r="I2350" s="91" t="s">
+      <c r="I2350" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97866,7 +97865,7 @@
       <c r="H2351">
         <v>0</v>
       </c>
-      <c r="I2351" s="91" t="s">
+      <c r="I2351" t="s">
         <v>12</v>
       </c>
     </row>
@@ -97895,7 +97894,7 @@
       <c r="H2352">
         <v>3</v>
       </c>
-      <c r="I2352" s="91" t="s">
+      <c r="I2352" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97924,7 +97923,7 @@
       <c r="H2353">
         <v>3</v>
       </c>
-      <c r="I2353" s="91" t="s">
+      <c r="I2353" t="s">
         <v>30</v>
       </c>
     </row>
@@ -97953,7 +97952,7 @@
       <c r="H2354">
         <v>1</v>
       </c>
-      <c r="I2354" s="91" t="s">
+      <c r="I2354" t="s">
         <v>17</v>
       </c>
     </row>
@@ -97982,7 +97981,7 @@
       <c r="H2355">
         <v>0</v>
       </c>
-      <c r="I2355" s="91" t="s">
+      <c r="I2355" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98011,7 +98010,7 @@
       <c r="H2356">
         <v>1</v>
       </c>
-      <c r="I2356" s="91" t="s">
+      <c r="I2356" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98040,7 +98039,7 @@
       <c r="H2357">
         <v>3</v>
       </c>
-      <c r="I2357" s="91" t="s">
+      <c r="I2357" t="s">
         <v>30</v>
       </c>
     </row>
@@ -98069,7 +98068,7 @@
       <c r="H2358">
         <v>0</v>
       </c>
-      <c r="I2358" s="91" t="s">
+      <c r="I2358" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98098,7 +98097,7 @@
       <c r="H2359">
         <v>0</v>
       </c>
-      <c r="I2359" s="91" t="s">
+      <c r="I2359" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98127,7 +98126,7 @@
       <c r="H2360">
         <v>0</v>
       </c>
-      <c r="I2360" s="91" t="s">
+      <c r="I2360" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98156,7 +98155,7 @@
       <c r="H2361">
         <v>0</v>
       </c>
-      <c r="I2361" s="91" t="s">
+      <c r="I2361" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98185,7 +98184,7 @@
       <c r="H2362">
         <v>1</v>
       </c>
-      <c r="I2362" s="91" t="s">
+      <c r="I2362" t="s">
         <v>30</v>
       </c>
     </row>
@@ -98214,7 +98213,7 @@
       <c r="H2363">
         <v>0</v>
       </c>
-      <c r="I2363" s="91" t="s">
+      <c r="I2363" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98243,7 +98242,7 @@
       <c r="H2364">
         <v>1</v>
       </c>
-      <c r="I2364" s="91" t="s">
+      <c r="I2364" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98272,7 +98271,7 @@
       <c r="H2365">
         <v>1</v>
       </c>
-      <c r="I2365" s="91" t="s">
+      <c r="I2365" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98301,7 +98300,7 @@
       <c r="H2366">
         <v>0</v>
       </c>
-      <c r="I2366" s="91" t="s">
+      <c r="I2366" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98330,7 +98329,7 @@
       <c r="H2367">
         <v>2</v>
       </c>
-      <c r="I2367" s="91" t="s">
+      <c r="I2367" t="s">
         <v>30</v>
       </c>
     </row>
@@ -98359,7 +98358,7 @@
       <c r="H2368">
         <v>0</v>
       </c>
-      <c r="I2368" s="91" t="s">
+      <c r="I2368" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98388,7 +98387,7 @@
       <c r="H2369">
         <v>1</v>
       </c>
-      <c r="I2369" s="91" t="s">
+      <c r="I2369" t="s">
         <v>17</v>
       </c>
     </row>
@@ -98417,7 +98416,7 @@
       <c r="H2370">
         <v>2</v>
       </c>
-      <c r="I2370" s="91" t="s">
+      <c r="I2370" t="s">
         <v>17</v>
       </c>
     </row>
@@ -98446,7 +98445,7 @@
       <c r="H2371">
         <v>0</v>
       </c>
-      <c r="I2371" s="91" t="s">
+      <c r="I2371" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98475,7 +98474,7 @@
       <c r="H2372">
         <v>0</v>
       </c>
-      <c r="I2372" s="91" t="s">
+      <c r="I2372" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98504,7 +98503,7 @@
       <c r="H2373">
         <v>0</v>
       </c>
-      <c r="I2373" s="91" t="s">
+      <c r="I2373" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98533,7 +98532,7 @@
       <c r="H2374">
         <v>2</v>
       </c>
-      <c r="I2374" s="91" t="s">
+      <c r="I2374" t="s">
         <v>17</v>
       </c>
     </row>
@@ -98562,7 +98561,7 @@
       <c r="H2375">
         <v>0</v>
       </c>
-      <c r="I2375" s="91" t="s">
+      <c r="I2375" t="s">
         <v>17</v>
       </c>
     </row>
@@ -98591,7 +98590,7 @@
       <c r="H2376">
         <v>0</v>
       </c>
-      <c r="I2376" s="91" t="s">
+      <c r="I2376" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98620,7 +98619,7 @@
       <c r="H2377">
         <v>0</v>
       </c>
-      <c r="I2377" s="91" t="s">
+      <c r="I2377" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98649,7 +98648,7 @@
       <c r="H2378">
         <v>0</v>
       </c>
-      <c r="I2378" s="91" t="s">
+      <c r="I2378" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98678,7 +98677,7 @@
       <c r="H2379">
         <v>0</v>
       </c>
-      <c r="I2379" s="91" t="s">
+      <c r="I2379" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98707,7 +98706,7 @@
       <c r="H2380">
         <v>2</v>
       </c>
-      <c r="I2380" s="91" t="s">
+      <c r="I2380" t="s">
         <v>17</v>
       </c>
     </row>
@@ -98736,7 +98735,7 @@
       <c r="H2381">
         <v>2</v>
       </c>
-      <c r="I2381" s="91" t="s">
+      <c r="I2381" t="s">
         <v>30</v>
       </c>
     </row>
@@ -98765,7 +98764,7 @@
       <c r="H2382">
         <v>1</v>
       </c>
-      <c r="I2382" s="91" t="s">
+      <c r="I2382" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98794,7 +98793,7 @@
       <c r="H2383">
         <v>1</v>
       </c>
-      <c r="I2383" s="91" t="s">
+      <c r="I2383" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98823,7 +98822,7 @@
       <c r="H2384">
         <v>1</v>
       </c>
-      <c r="I2384" s="91" t="s">
+      <c r="I2384" t="s">
         <v>17</v>
       </c>
     </row>
@@ -98852,7 +98851,7 @@
       <c r="H2385">
         <v>0</v>
       </c>
-      <c r="I2385" s="91" t="s">
+      <c r="I2385" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98881,7 +98880,7 @@
       <c r="H2386">
         <v>3</v>
       </c>
-      <c r="I2386" s="91" t="s">
+      <c r="I2386" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98910,7 +98909,7 @@
       <c r="H2387">
         <v>2</v>
       </c>
-      <c r="I2387" s="91" t="s">
+      <c r="I2387" t="s">
         <v>30</v>
       </c>
     </row>
@@ -98939,7 +98938,7 @@
       <c r="H2388">
         <v>1</v>
       </c>
-      <c r="I2388" s="91" t="s">
+      <c r="I2388" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98968,7 +98967,7 @@
       <c r="H2389">
         <v>0</v>
       </c>
-      <c r="I2389" s="91" t="s">
+      <c r="I2389" t="s">
         <v>12</v>
       </c>
     </row>
@@ -98997,7 +98996,7 @@
       <c r="H2390">
         <v>2</v>
       </c>
-      <c r="I2390" s="91" t="s">
+      <c r="I2390" t="s">
         <v>30</v>
       </c>
     </row>
@@ -99026,7 +99025,7 @@
       <c r="H2391">
         <v>1</v>
       </c>
-      <c r="I2391" s="91" t="s">
+      <c r="I2391" t="s">
         <v>17</v>
       </c>
     </row>
@@ -99055,7 +99054,7 @@
       <c r="H2392">
         <v>0</v>
       </c>
-      <c r="I2392" s="91" t="s">
+      <c r="I2392" t="s">
         <v>12</v>
       </c>
     </row>
@@ -99084,7 +99083,7 @@
       <c r="H2393">
         <v>1</v>
       </c>
-      <c r="I2393" s="91" t="s">
+      <c r="I2393" t="s">
         <v>30</v>
       </c>
     </row>
@@ -99113,7 +99112,7 @@
       <c r="H2394">
         <v>2</v>
       </c>
-      <c r="I2394" s="91" t="s">
+      <c r="I2394" t="s">
         <v>17</v>
       </c>
     </row>
@@ -99142,7 +99141,7 @@
       <c r="H2395">
         <v>1</v>
       </c>
-      <c r="I2395" s="91" t="s">
+      <c r="I2395" t="s">
         <v>12</v>
       </c>
     </row>
@@ -99171,7 +99170,7 @@
       <c r="H2396">
         <v>1</v>
       </c>
-      <c r="I2396" s="91" t="s">
+      <c r="I2396" t="s">
         <v>30</v>
       </c>
     </row>
@@ -99200,7 +99199,7 @@
       <c r="H2397">
         <v>0</v>
       </c>
-      <c r="I2397" s="91" t="s">
+      <c r="I2397" t="s">
         <v>17</v>
       </c>
     </row>
@@ -99229,7 +99228,7 @@
       <c r="H2398">
         <v>1</v>
       </c>
-      <c r="I2398" s="91" t="s">
+      <c r="I2398" t="s">
         <v>17</v>
       </c>
     </row>
@@ -99258,7 +99257,7 @@
       <c r="H2399">
         <v>0</v>
       </c>
-      <c r="I2399" s="91" t="s">
+      <c r="I2399" t="s">
         <v>12</v>
       </c>
     </row>
@@ -99287,12 +99286,12 @@
       <c r="H2400">
         <v>0</v>
       </c>
-      <c r="I2400" s="91" t="s">
+      <c r="I2400" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2194" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I2400" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -99315,42 +99314,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="80" t="s">
+      <c r="E2" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="80" t="s">
+      <c r="F2" s="86"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="81"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="80" t="s">
+      <c r="I2" s="86"/>
+      <c r="J2" s="87"/>
+      <c r="K2" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="81"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="80" t="s">
+      <c r="L2" s="86"/>
+      <c r="M2" s="87"/>
+      <c r="N2" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="81"/>
-      <c r="P2" s="82"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="87"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="74"/>
-      <c r="C3" s="74" t="s">
+      <c r="B3" s="88"/>
+      <c r="C3" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="75"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="30" t="s">
         <v>47</v>
       </c>
@@ -99859,69 +99858,69 @@
       </c>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="79">
+      <c r="C14" s="79"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="81">
         <v>0.3</v>
       </c>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="71">
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="83">
         <v>0.4</v>
       </c>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="71">
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="83">
         <v>0.5</v>
       </c>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="71">
+      <c r="L14" s="82"/>
+      <c r="M14" s="82"/>
+      <c r="N14" s="83">
         <v>0.6</v>
       </c>
-      <c r="O14" s="72"/>
-      <c r="P14" s="73"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="84"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="80" t="s">
+      <c r="E16" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="81"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="80" t="s">
+      <c r="F16" s="86"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="81"/>
-      <c r="J16" s="82"/>
-      <c r="K16" s="80" t="s">
+      <c r="I16" s="86"/>
+      <c r="J16" s="87"/>
+      <c r="K16" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="L16" s="81"/>
-      <c r="M16" s="82"/>
-      <c r="N16" s="80" t="s">
+      <c r="L16" s="86"/>
+      <c r="M16" s="87"/>
+      <c r="N16" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="81"/>
-      <c r="P16" s="82"/>
+      <c r="O16" s="86"/>
+      <c r="P16" s="87"/>
     </row>
     <row r="17" spans="2:16">
-      <c r="B17" s="74"/>
-      <c r="C17" s="74" t="s">
+      <c r="B17" s="88"/>
+      <c r="C17" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="75"/>
+      <c r="D17" s="89"/>
       <c r="E17" s="30" t="s">
         <v>47</v>
       </c>
@@ -100430,31 +100429,31 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="76" t="s">
+      <c r="B28" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="79">
+      <c r="C28" s="79"/>
+      <c r="D28" s="80"/>
+      <c r="E28" s="81">
         <v>0.7</v>
       </c>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="71">
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="83">
         <v>0.4</v>
       </c>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="71">
+      <c r="I28" s="82"/>
+      <c r="J28" s="82"/>
+      <c r="K28" s="83">
         <v>0.5</v>
       </c>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="71">
+      <c r="L28" s="82"/>
+      <c r="M28" s="82"/>
+      <c r="N28" s="83">
         <v>0.5</v>
       </c>
-      <c r="O28" s="72"/>
-      <c r="P28" s="73"/>
+      <c r="O28" s="82"/>
+      <c r="P28" s="84"/>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" s="32" t="s">
@@ -100927,31 +100926,31 @@
       </c>
     </row>
     <row r="40" spans="2:19">
-      <c r="B40" s="76" t="s">
+      <c r="B40" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="77"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="79">
+      <c r="C40" s="79"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="81">
         <v>0.7</v>
       </c>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="71">
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="83">
         <v>0.8</v>
       </c>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="71">
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="83">
         <v>0.7</v>
       </c>
-      <c r="L40" s="72"/>
-      <c r="M40" s="72"/>
-      <c r="N40" s="71">
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="83">
         <v>0.7</v>
       </c>
-      <c r="O40" s="72"/>
-      <c r="P40" s="73"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="84"/>
     </row>
     <row r="42" spans="2:19">
       <c r="B42" s="32" t="s">
@@ -101428,64 +101427,64 @@
       </c>
     </row>
     <row r="52" spans="2:16">
-      <c r="B52" s="76" t="s">
+      <c r="B52" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="77"/>
-      <c r="D52" s="78"/>
-      <c r="E52" s="79">
+      <c r="C52" s="79"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="81">
         <v>0.2</v>
       </c>
-      <c r="F52" s="72"/>
-      <c r="G52" s="72"/>
-      <c r="H52" s="71">
+      <c r="F52" s="82"/>
+      <c r="G52" s="82"/>
+      <c r="H52" s="83">
         <v>0.5</v>
       </c>
-      <c r="I52" s="72"/>
-      <c r="J52" s="72"/>
-      <c r="K52" s="71">
+      <c r="I52" s="82"/>
+      <c r="J52" s="82"/>
+      <c r="K52" s="83">
         <v>0.4</v>
       </c>
-      <c r="L52" s="72"/>
-      <c r="M52" s="72"/>
-      <c r="N52" s="71">
+      <c r="L52" s="82"/>
+      <c r="M52" s="82"/>
+      <c r="N52" s="83">
         <v>0.3</v>
       </c>
-      <c r="O52" s="72"/>
-      <c r="P52" s="73"/>
+      <c r="O52" s="82"/>
+      <c r="P52" s="84"/>
     </row>
     <row r="54" spans="2:16">
-      <c r="B54" s="74" t="s">
+      <c r="B54" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="74" t="s">
+      <c r="C54" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="75" t="s">
+      <c r="D54" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="80" t="s">
+      <c r="E54" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="81"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="80" t="s">
+      <c r="F54" s="86"/>
+      <c r="G54" s="87"/>
+      <c r="H54" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="I54" s="81"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="80" t="s">
+      <c r="I54" s="86"/>
+      <c r="J54" s="87"/>
+      <c r="K54" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="81"/>
-      <c r="M54" s="82"/>
+      <c r="L54" s="86"/>
+      <c r="M54" s="87"/>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="74"/>
-      <c r="C55" s="74" t="s">
+      <c r="B55" s="88"/>
+      <c r="C55" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="75"/>
+      <c r="D55" s="89"/>
       <c r="E55" s="30" t="s">
         <v>47</v>
       </c>
@@ -101895,59 +101894,59 @@
       </c>
     </row>
     <row r="66" spans="2:13">
-      <c r="B66" s="76" t="s">
+      <c r="B66" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="77"/>
-      <c r="D66" s="78"/>
-      <c r="E66" s="79">
+      <c r="C66" s="79"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="81">
         <v>0.7</v>
       </c>
-      <c r="F66" s="72"/>
-      <c r="G66" s="72"/>
-      <c r="H66" s="71">
+      <c r="F66" s="82"/>
+      <c r="G66" s="82"/>
+      <c r="H66" s="83">
         <v>0.7</v>
       </c>
-      <c r="I66" s="72"/>
-      <c r="J66" s="72"/>
-      <c r="K66" s="71">
+      <c r="I66" s="82"/>
+      <c r="J66" s="82"/>
+      <c r="K66" s="83">
         <v>0.7</v>
       </c>
-      <c r="L66" s="72"/>
-      <c r="M66" s="73"/>
+      <c r="L66" s="82"/>
+      <c r="M66" s="84"/>
     </row>
     <row r="68" spans="2:13">
-      <c r="B68" s="74" t="s">
+      <c r="B68" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="74" t="s">
+      <c r="C68" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D68" s="75" t="s">
+      <c r="D68" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="E68" s="80" t="s">
+      <c r="E68" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="81"/>
-      <c r="G68" s="82"/>
-      <c r="H68" s="80" t="s">
+      <c r="F68" s="86"/>
+      <c r="G68" s="87"/>
+      <c r="H68" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="I68" s="81"/>
-      <c r="J68" s="82"/>
-      <c r="K68" s="80" t="s">
+      <c r="I68" s="86"/>
+      <c r="J68" s="87"/>
+      <c r="K68" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="L68" s="81"/>
-      <c r="M68" s="82"/>
+      <c r="L68" s="86"/>
+      <c r="M68" s="87"/>
     </row>
     <row r="69" spans="2:13">
-      <c r="B69" s="74"/>
-      <c r="C69" s="74" t="s">
+      <c r="B69" s="88"/>
+      <c r="C69" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D69" s="75"/>
+      <c r="D69" s="89"/>
       <c r="E69" s="30" t="s">
         <v>47</v>
       </c>
@@ -102357,54 +102356,54 @@
       </c>
     </row>
     <row r="80" spans="2:13">
-      <c r="B80" s="76" t="s">
+      <c r="B80" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C80" s="77"/>
-      <c r="D80" s="78"/>
-      <c r="E80" s="79">
+      <c r="C80" s="79"/>
+      <c r="D80" s="80"/>
+      <c r="E80" s="81">
         <v>0.4</v>
       </c>
-      <c r="F80" s="72"/>
-      <c r="G80" s="72"/>
-      <c r="H80" s="71">
+      <c r="F80" s="82"/>
+      <c r="G80" s="82"/>
+      <c r="H80" s="83">
         <v>0.3</v>
       </c>
-      <c r="I80" s="72"/>
-      <c r="J80" s="72"/>
-      <c r="K80" s="71">
+      <c r="I80" s="82"/>
+      <c r="J80" s="82"/>
+      <c r="K80" s="83">
         <v>0.5</v>
       </c>
-      <c r="L80" s="72"/>
-      <c r="M80" s="73"/>
+      <c r="L80" s="82"/>
+      <c r="M80" s="84"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="74" t="s">
+      <c r="B82" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C82" s="74" t="s">
+      <c r="C82" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D82" s="75" t="s">
+      <c r="D82" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="E82" s="80" t="s">
+      <c r="E82" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="81"/>
-      <c r="G82" s="81"/>
-      <c r="H82" s="83" t="s">
+      <c r="F82" s="86"/>
+      <c r="G82" s="86"/>
+      <c r="H82" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="I82" s="81"/>
-      <c r="J82" s="84"/>
+      <c r="I82" s="86"/>
+      <c r="J82" s="91"/>
     </row>
     <row r="83" spans="2:13">
-      <c r="B83" s="74"/>
-      <c r="C83" s="74" t="s">
+      <c r="B83" s="88"/>
+      <c r="C83" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D83" s="75"/>
+      <c r="D83" s="89"/>
       <c r="E83" s="30" t="s">
         <v>47</v>
       </c>
@@ -102541,21 +102540,21 @@
       </c>
     </row>
     <row r="88" spans="2:13">
-      <c r="B88" s="76" t="s">
+      <c r="B88" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C88" s="77"/>
-      <c r="D88" s="78"/>
-      <c r="E88" s="79">
+      <c r="C88" s="79"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="81">
         <v>0.75</v>
       </c>
-      <c r="F88" s="72"/>
-      <c r="G88" s="72"/>
-      <c r="H88" s="71">
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="83">
         <v>0.75</v>
       </c>
-      <c r="I88" s="72"/>
-      <c r="J88" s="73"/>
+      <c r="I88" s="82"/>
+      <c r="J88" s="84"/>
     </row>
     <row r="89" spans="2:13">
       <c r="B89" s="32" t="s">
@@ -102692,26 +102691,26 @@
       <c r="M92" s="18"/>
     </row>
     <row r="93" spans="2:13">
-      <c r="B93" s="76" t="s">
+      <c r="B93" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C93" s="77"/>
-      <c r="D93" s="78"/>
-      <c r="E93" s="79">
+      <c r="C93" s="79"/>
+      <c r="D93" s="80"/>
+      <c r="E93" s="81">
         <v>0.75</v>
       </c>
-      <c r="F93" s="72"/>
-      <c r="G93" s="72"/>
-      <c r="H93" s="71">
+      <c r="F93" s="82"/>
+      <c r="G93" s="82"/>
+      <c r="H93" s="83">
         <v>0.5</v>
       </c>
-      <c r="I93" s="72"/>
-      <c r="J93" s="73"/>
-      <c r="K93" s="71">
-        <v>0</v>
-      </c>
-      <c r="L93" s="72"/>
-      <c r="M93" s="73"/>
+      <c r="I93" s="82"/>
+      <c r="J93" s="84"/>
+      <c r="K93" s="83">
+        <v>0</v>
+      </c>
+      <c r="L93" s="82"/>
+      <c r="M93" s="84"/>
     </row>
     <row r="94" spans="2:13">
       <c r="B94" s="32" t="s">
@@ -102830,49 +102829,49 @@
       </c>
     </row>
     <row r="98" spans="2:10">
-      <c r="B98" s="76" t="s">
+      <c r="B98" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C98" s="77"/>
-      <c r="D98" s="78"/>
-      <c r="E98" s="79">
+      <c r="C98" s="79"/>
+      <c r="D98" s="80"/>
+      <c r="E98" s="81">
         <v>0.25</v>
       </c>
-      <c r="F98" s="72"/>
-      <c r="G98" s="72"/>
-      <c r="H98" s="71">
+      <c r="F98" s="82"/>
+      <c r="G98" s="82"/>
+      <c r="H98" s="83">
         <v>0.5</v>
       </c>
-      <c r="I98" s="72"/>
-      <c r="J98" s="73"/>
+      <c r="I98" s="82"/>
+      <c r="J98" s="84"/>
     </row>
     <row r="100" spans="2:10">
-      <c r="B100" s="74" t="s">
+      <c r="B100" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C100" s="74" t="s">
+      <c r="C100" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="75" t="s">
+      <c r="D100" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="E100" s="80" t="s">
+      <c r="E100" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="81"/>
-      <c r="G100" s="81"/>
-      <c r="H100" s="83" t="s">
+      <c r="F100" s="86"/>
+      <c r="G100" s="86"/>
+      <c r="H100" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="I100" s="81"/>
-      <c r="J100" s="84"/>
+      <c r="I100" s="86"/>
+      <c r="J100" s="91"/>
     </row>
     <row r="101" spans="2:10">
-      <c r="B101" s="74"/>
-      <c r="C101" s="74" t="s">
+      <c r="B101" s="88"/>
+      <c r="C101" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="75"/>
+      <c r="D101" s="89"/>
       <c r="E101" s="30" t="s">
         <v>47</v>
       </c>
@@ -103009,21 +103008,21 @@
       </c>
     </row>
     <row r="106" spans="2:10">
-      <c r="B106" s="76" t="s">
+      <c r="B106" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C106" s="77"/>
-      <c r="D106" s="78"/>
-      <c r="E106" s="79">
+      <c r="C106" s="79"/>
+      <c r="D106" s="80"/>
+      <c r="E106" s="81">
         <v>0.5</v>
       </c>
-      <c r="F106" s="72"/>
-      <c r="G106" s="72"/>
-      <c r="H106" s="71">
+      <c r="F106" s="82"/>
+      <c r="G106" s="82"/>
+      <c r="H106" s="83">
         <v>0.75</v>
       </c>
-      <c r="I106" s="72"/>
-      <c r="J106" s="73"/>
+      <c r="I106" s="82"/>
+      <c r="J106" s="84"/>
     </row>
     <row r="107" spans="2:10">
       <c r="B107" s="32" t="s">
@@ -103142,21 +103141,21 @@
       </c>
     </row>
     <row r="111" spans="2:10">
-      <c r="B111" s="76" t="s">
+      <c r="B111" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C111" s="77"/>
-      <c r="D111" s="78"/>
-      <c r="E111" s="79">
+      <c r="C111" s="79"/>
+      <c r="D111" s="80"/>
+      <c r="E111" s="81">
         <v>0.25</v>
       </c>
-      <c r="F111" s="72"/>
-      <c r="G111" s="72"/>
-      <c r="H111" s="71">
+      <c r="F111" s="82"/>
+      <c r="G111" s="82"/>
+      <c r="H111" s="83">
         <v>0.75</v>
       </c>
-      <c r="I111" s="72"/>
-      <c r="J111" s="73"/>
+      <c r="I111" s="82"/>
+      <c r="J111" s="84"/>
     </row>
     <row r="112" spans="2:10">
       <c r="B112" s="32" t="s">
@@ -103275,21 +103274,21 @@
       </c>
     </row>
     <row r="116" spans="2:23">
-      <c r="B116" s="76" t="s">
+      <c r="B116" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C116" s="77"/>
-      <c r="D116" s="78"/>
-      <c r="E116" s="79">
+      <c r="C116" s="79"/>
+      <c r="D116" s="80"/>
+      <c r="E116" s="81">
         <v>0.25</v>
       </c>
-      <c r="F116" s="72"/>
-      <c r="G116" s="72"/>
-      <c r="H116" s="71">
+      <c r="F116" s="82"/>
+      <c r="G116" s="82"/>
+      <c r="H116" s="83">
         <v>0.5</v>
       </c>
-      <c r="I116" s="72"/>
-      <c r="J116" s="73"/>
+      <c r="I116" s="82"/>
+      <c r="J116" s="84"/>
     </row>
     <row r="121" spans="2:23">
       <c r="B121" s="62" t="s">
@@ -103301,21 +103300,21 @@
       <c r="D121" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E121" s="80" t="s">
+      <c r="E121" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="F121" s="81"/>
-      <c r="G121" s="82"/>
-      <c r="H121" s="80" t="s">
+      <c r="F121" s="86"/>
+      <c r="G121" s="87"/>
+      <c r="H121" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="I121" s="81"/>
-      <c r="J121" s="82"/>
-      <c r="K121" s="80" t="s">
+      <c r="I121" s="86"/>
+      <c r="J121" s="87"/>
+      <c r="K121" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="L121" s="81"/>
-      <c r="M121" s="82"/>
+      <c r="L121" s="86"/>
+      <c r="M121" s="87"/>
       <c r="R121" s="59" t="s">
         <v>4</v>
       </c>
@@ -103345,21 +103344,21 @@
       <c r="D122" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E122" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="86"/>
-      <c r="G122" s="87"/>
-      <c r="H122" s="85" t="s">
+      <c r="E122" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="73"/>
+      <c r="G122" s="74"/>
+      <c r="H122" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="I122" s="86"/>
-      <c r="J122" s="87"/>
-      <c r="K122" s="85" t="s">
+      <c r="I122" s="73"/>
+      <c r="J122" s="74"/>
+      <c r="K122" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="L122" s="86"/>
-      <c r="M122" s="87"/>
+      <c r="L122" s="73"/>
+      <c r="M122" s="74"/>
       <c r="R122" s="32" t="s">
         <v>11</v>
       </c>
@@ -103389,21 +103388,21 @@
       <c r="D123" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E123" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" s="89"/>
-      <c r="G123" s="90"/>
-      <c r="H123" s="88" t="s">
+      <c r="E123" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F123" s="76"/>
+      <c r="G123" s="77"/>
+      <c r="H123" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="I123" s="89"/>
-      <c r="J123" s="90"/>
-      <c r="K123" s="88" t="s">
+      <c r="I123" s="76"/>
+      <c r="J123" s="77"/>
+      <c r="K123" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="L123" s="89"/>
-      <c r="M123" s="90"/>
+      <c r="L123" s="76"/>
+      <c r="M123" s="77"/>
       <c r="R123" s="34" t="s">
         <v>22</v>
       </c>
@@ -103433,21 +103432,21 @@
       <c r="D124" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E124" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="86"/>
-      <c r="G124" s="87"/>
-      <c r="H124" s="85" t="s">
+      <c r="E124" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="73"/>
+      <c r="G124" s="74"/>
+      <c r="H124" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="I124" s="86"/>
-      <c r="J124" s="87"/>
-      <c r="K124" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="L124" s="86"/>
-      <c r="M124" s="87"/>
+      <c r="I124" s="73"/>
+      <c r="J124" s="74"/>
+      <c r="K124" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L124" s="73"/>
+      <c r="M124" s="74"/>
       <c r="R124" s="35" t="s">
         <v>18</v>
       </c>
@@ -103477,21 +103476,21 @@
       <c r="D125" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E125" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="89"/>
-      <c r="G125" s="90"/>
-      <c r="H125" s="88" t="s">
+      <c r="E125" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="76"/>
+      <c r="G125" s="77"/>
+      <c r="H125" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="I125" s="89"/>
-      <c r="J125" s="90"/>
-      <c r="K125" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="L125" s="89"/>
-      <c r="M125" s="90"/>
+      <c r="I125" s="76"/>
+      <c r="J125" s="77"/>
+      <c r="K125" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="L125" s="76"/>
+      <c r="M125" s="77"/>
       <c r="R125" s="34" t="s">
         <v>23</v>
       </c>
@@ -103521,21 +103520,21 @@
       <c r="D126" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E126" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="86"/>
-      <c r="G126" s="87"/>
-      <c r="H126" s="85" t="s">
+      <c r="E126" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="73"/>
+      <c r="G126" s="74"/>
+      <c r="H126" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="I126" s="86"/>
-      <c r="J126" s="87"/>
-      <c r="K126" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="L126" s="86"/>
-      <c r="M126" s="87"/>
+      <c r="I126" s="73"/>
+      <c r="J126" s="74"/>
+      <c r="K126" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L126" s="73"/>
+      <c r="M126" s="74"/>
       <c r="R126" s="35" t="s">
         <v>29</v>
       </c>
@@ -103565,21 +103564,21 @@
       <c r="D127" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E127" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="89"/>
-      <c r="G127" s="90"/>
-      <c r="H127" s="88" t="s">
+      <c r="E127" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="76"/>
+      <c r="G127" s="77"/>
+      <c r="H127" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="I127" s="89"/>
-      <c r="J127" s="90"/>
-      <c r="K127" s="88" t="s">
+      <c r="I127" s="76"/>
+      <c r="J127" s="77"/>
+      <c r="K127" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="L127" s="89"/>
-      <c r="M127" s="90"/>
+      <c r="L127" s="76"/>
+      <c r="M127" s="77"/>
       <c r="R127" s="34" t="s">
         <v>27</v>
       </c>
@@ -103609,21 +103608,21 @@
       <c r="D128" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E128" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" s="86"/>
-      <c r="G128" s="87"/>
-      <c r="H128" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="I128" s="86"/>
-      <c r="J128" s="87"/>
-      <c r="K128" s="85" t="s">
+      <c r="E128" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="73"/>
+      <c r="G128" s="74"/>
+      <c r="H128" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I128" s="73"/>
+      <c r="J128" s="74"/>
+      <c r="K128" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="L128" s="86"/>
-      <c r="M128" s="87"/>
+      <c r="L128" s="73"/>
+      <c r="M128" s="74"/>
       <c r="R128" s="35" t="s">
         <v>38</v>
       </c>
@@ -103653,21 +103652,21 @@
       <c r="D129" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E129" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129" s="89"/>
-      <c r="G129" s="90"/>
-      <c r="H129" s="88" t="s">
+      <c r="E129" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="76"/>
+      <c r="G129" s="77"/>
+      <c r="H129" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="I129" s="89"/>
-      <c r="J129" s="90"/>
-      <c r="K129" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="L129" s="89"/>
-      <c r="M129" s="90"/>
+      <c r="I129" s="76"/>
+      <c r="J129" s="77"/>
+      <c r="K129" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="L129" s="76"/>
+      <c r="M129" s="77"/>
       <c r="R129" s="34" t="s">
         <v>24</v>
       </c>
@@ -103697,21 +103696,21 @@
       <c r="D130" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E130" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="F130" s="86"/>
-      <c r="G130" s="87"/>
-      <c r="H130" s="85" t="s">
+      <c r="E130" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="73"/>
+      <c r="G130" s="74"/>
+      <c r="H130" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="I130" s="86"/>
-      <c r="J130" s="87"/>
-      <c r="K130" s="85" t="s">
-        <v>12</v>
-      </c>
-      <c r="L130" s="86"/>
-      <c r="M130" s="87"/>
+      <c r="I130" s="73"/>
+      <c r="J130" s="74"/>
+      <c r="K130" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L130" s="73"/>
+      <c r="M130" s="74"/>
       <c r="R130" s="36" t="s">
         <v>50</v>
       </c>
@@ -103741,21 +103740,21 @@
       <c r="D131" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E131" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="89"/>
-      <c r="G131" s="90"/>
-      <c r="H131" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="I131" s="89"/>
-      <c r="J131" s="90"/>
-      <c r="K131" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="L131" s="89"/>
-      <c r="M131" s="90"/>
+      <c r="E131" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="76"/>
+      <c r="G131" s="77"/>
+      <c r="H131" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="I131" s="76"/>
+      <c r="J131" s="77"/>
+      <c r="K131" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="L131" s="76"/>
+      <c r="M131" s="77"/>
       <c r="R131" s="34" t="s">
         <v>19</v>
       </c>
@@ -103776,31 +103775,31 @@
       </c>
     </row>
     <row r="132" spans="2:23">
-      <c r="B132" s="76" t="s">
+      <c r="B132" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C132" s="77"/>
-      <c r="D132" s="78"/>
-      <c r="E132" s="79">
+      <c r="C132" s="79"/>
+      <c r="D132" s="80"/>
+      <c r="E132" s="81">
         <v>0.7</v>
       </c>
-      <c r="F132" s="72"/>
-      <c r="G132" s="72"/>
-      <c r="H132" s="71">
+      <c r="F132" s="82"/>
+      <c r="G132" s="82"/>
+      <c r="H132" s="83">
         <v>0.2</v>
       </c>
-      <c r="I132" s="72"/>
-      <c r="J132" s="72"/>
-      <c r="K132" s="71">
+      <c r="I132" s="82"/>
+      <c r="J132" s="82"/>
+      <c r="K132" s="83">
         <v>0.8</v>
       </c>
-      <c r="L132" s="72"/>
-      <c r="M132" s="73"/>
-      <c r="R132" s="76" t="s">
+      <c r="L132" s="82"/>
+      <c r="M132" s="84"/>
+      <c r="R132" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="S132" s="77"/>
-      <c r="T132" s="78"/>
+      <c r="S132" s="79"/>
+      <c r="T132" s="80"/>
       <c r="U132" s="57">
         <v>0.7</v>
       </c>
@@ -103813,20 +103812,89 @@
     </row>
   </sheetData>
   <mergeCells count="121">
-    <mergeCell ref="K122:M122"/>
-    <mergeCell ref="K123:M123"/>
-    <mergeCell ref="K124:M124"/>
-    <mergeCell ref="K125:M125"/>
-    <mergeCell ref="K126:M126"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="H130:J130"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="R132:T132"/>
-    <mergeCell ref="K127:M127"/>
-    <mergeCell ref="K128:M128"/>
-    <mergeCell ref="K129:M129"/>
-    <mergeCell ref="K130:M130"/>
-    <mergeCell ref="K131:M131"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:M28"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="H88:J88"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="H100:J100"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="H116:J116"/>
+    <mergeCell ref="K93:M93"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E111:G111"/>
+    <mergeCell ref="H111:J111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="E106:G106"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="H98:J98"/>
     <mergeCell ref="B132:D132"/>
     <mergeCell ref="E132:G132"/>
     <mergeCell ref="H132:J132"/>
@@ -103851,89 +103919,20 @@
     <mergeCell ref="H126:J126"/>
     <mergeCell ref="H127:J127"/>
     <mergeCell ref="H128:J128"/>
-    <mergeCell ref="B116:D116"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="H116:J116"/>
-    <mergeCell ref="K93:M93"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E111:G111"/>
-    <mergeCell ref="H111:J111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="E106:G106"/>
-    <mergeCell ref="H106:J106"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="H98:J98"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="H88:J88"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="H100:J100"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="H93:J93"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="K68:M68"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="K28:M28"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="K122:M122"/>
+    <mergeCell ref="K123:M123"/>
+    <mergeCell ref="K124:M124"/>
+    <mergeCell ref="K125:M125"/>
+    <mergeCell ref="K126:M126"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="H130:J130"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="R132:T132"/>
+    <mergeCell ref="K127:M127"/>
+    <mergeCell ref="K128:M128"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="K130:M130"/>
+    <mergeCell ref="K131:M131"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -103952,7 +103951,7 @@
       <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="92">
+      <c r="B1" s="71">
         <v>2026</v>
       </c>
     </row>
@@ -103968,7 +103967,7 @@
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="91">
+      <c r="B4">
         <v>61</v>
       </c>
     </row>
@@ -103976,7 +103975,7 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="91">
+      <c r="B5">
         <v>99</v>
       </c>
     </row>
@@ -103984,7 +103983,7 @@
       <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="91">
+      <c r="B6">
         <v>44</v>
       </c>
     </row>
@@ -103992,7 +103991,7 @@
       <c r="A7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="91">
+      <c r="B7">
         <v>204</v>
       </c>
     </row>

--- a/TFE_PRONOSTICO/DATOS_LIGA_COLOMBIANA.xlsx
+++ b/TFE_PRONOSTICO/DATOS_LIGA_COLOMBIANA.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30404"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="979" documentId="8_{BD6864F7-2D08-4823-8130-8AEB370B13DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F1A26BE-ECCF-4753-B6E3-28ADC8585D6F}"/>
+  <xr:revisionPtr revIDLastSave="981" documentId="8_{BD6864F7-2D08-4823-8130-8AEB370B13DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42260CE0-1D9D-42F4-BFBA-2C89E1FBA774}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="1306" r:id="rId4"/>
+    <pivotCache cacheId="598" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -872,23 +872,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -911,26 +908,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -27454,7 +27454,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F97A265-E442-4D37-A950-2A2116028FDB}" name="Tabla dinámica1" cacheId="1306" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1F97A265-E442-4D37-A950-2A2116028FDB}" name="Tabla dinámica1" cacheId="598" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
@@ -35298,7 +35298,7 @@
         <v>18</v>
       </c>
       <c r="F255" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G255">
         <v>1</v>
@@ -35327,7 +35327,7 @@
         <v>24</v>
       </c>
       <c r="F256" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G256">
         <v>1</v>
@@ -99314,42 +99314,42 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="86"/>
-      <c r="G2" s="87"/>
-      <c r="H2" s="85" t="s">
+      <c r="F2" s="75"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="86"/>
-      <c r="J2" s="87"/>
-      <c r="K2" s="85" t="s">
+      <c r="I2" s="75"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="86"/>
-      <c r="M2" s="87"/>
-      <c r="N2" s="85" t="s">
+      <c r="L2" s="75"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="87"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="76"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="88"/>
-      <c r="C3" s="88" t="s">
+      <c r="B3" s="72"/>
+      <c r="C3" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="89"/>
+      <c r="D3" s="73"/>
       <c r="E3" s="30" t="s">
         <v>47</v>
       </c>
@@ -99858,69 +99858,69 @@
       </c>
     </row>
     <row r="14" spans="2:16">
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="81">
+      <c r="C14" s="78"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="80">
         <v>0.3</v>
       </c>
-      <c r="F14" s="82"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="83">
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="82">
         <v>0.4</v>
       </c>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="83">
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="82">
         <v>0.5</v>
       </c>
-      <c r="L14" s="82"/>
-      <c r="M14" s="82"/>
-      <c r="N14" s="83">
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="82">
         <v>0.6</v>
       </c>
-      <c r="O14" s="82"/>
-      <c r="P14" s="84"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="83"/>
     </row>
     <row r="16" spans="2:16">
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="85" t="s">
+      <c r="E16" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="86"/>
-      <c r="G16" s="87"/>
-      <c r="H16" s="85" t="s">
+      <c r="F16" s="75"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="86"/>
-      <c r="J16" s="87"/>
-      <c r="K16" s="85" t="s">
+      <c r="I16" s="75"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="L16" s="86"/>
-      <c r="M16" s="87"/>
-      <c r="N16" s="85" t="s">
+      <c r="L16" s="75"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="O16" s="86"/>
-      <c r="P16" s="87"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="76"/>
     </row>
     <row r="17" spans="2:16">
-      <c r="B17" s="88"/>
-      <c r="C17" s="88" t="s">
+      <c r="B17" s="72"/>
+      <c r="C17" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="89"/>
+      <c r="D17" s="73"/>
       <c r="E17" s="30" t="s">
         <v>47</v>
       </c>
@@ -100429,31 +100429,31 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="81">
+      <c r="C28" s="78"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="80">
         <v>0.7</v>
       </c>
-      <c r="F28" s="82"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="83">
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="82">
         <v>0.4</v>
       </c>
-      <c r="I28" s="82"/>
-      <c r="J28" s="82"/>
-      <c r="K28" s="83">
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="82">
         <v>0.5</v>
       </c>
-      <c r="L28" s="82"/>
-      <c r="M28" s="82"/>
-      <c r="N28" s="83">
+      <c r="L28" s="81"/>
+      <c r="M28" s="81"/>
+      <c r="N28" s="82">
         <v>0.5</v>
       </c>
-      <c r="O28" s="82"/>
-      <c r="P28" s="84"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="83"/>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" s="32" t="s">
@@ -100926,31 +100926,31 @@
       </c>
     </row>
     <row r="40" spans="2:19">
-      <c r="B40" s="78" t="s">
+      <c r="B40" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="79"/>
-      <c r="D40" s="80"/>
-      <c r="E40" s="81">
+      <c r="C40" s="78"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="80">
         <v>0.7</v>
       </c>
-      <c r="F40" s="82"/>
-      <c r="G40" s="82"/>
-      <c r="H40" s="83">
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="82">
         <v>0.8</v>
       </c>
-      <c r="I40" s="82"/>
-      <c r="J40" s="82"/>
-      <c r="K40" s="83">
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="82">
         <v>0.7</v>
       </c>
-      <c r="L40" s="82"/>
-      <c r="M40" s="82"/>
-      <c r="N40" s="83">
+      <c r="L40" s="81"/>
+      <c r="M40" s="81"/>
+      <c r="N40" s="82">
         <v>0.7</v>
       </c>
-      <c r="O40" s="82"/>
-      <c r="P40" s="84"/>
+      <c r="O40" s="81"/>
+      <c r="P40" s="83"/>
     </row>
     <row r="42" spans="2:19">
       <c r="B42" s="32" t="s">
@@ -101427,64 +101427,64 @@
       </c>
     </row>
     <row r="52" spans="2:16">
-      <c r="B52" s="78" t="s">
+      <c r="B52" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C52" s="79"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="81">
+      <c r="C52" s="78"/>
+      <c r="D52" s="79"/>
+      <c r="E52" s="80">
         <v>0.2</v>
       </c>
-      <c r="F52" s="82"/>
-      <c r="G52" s="82"/>
-      <c r="H52" s="83">
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="82">
         <v>0.5</v>
       </c>
-      <c r="I52" s="82"/>
-      <c r="J52" s="82"/>
-      <c r="K52" s="83">
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="82">
         <v>0.4</v>
       </c>
-      <c r="L52" s="82"/>
-      <c r="M52" s="82"/>
-      <c r="N52" s="83">
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="82">
         <v>0.3</v>
       </c>
-      <c r="O52" s="82"/>
-      <c r="P52" s="84"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="83"/>
     </row>
     <row r="54" spans="2:16">
-      <c r="B54" s="88" t="s">
+      <c r="B54" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C54" s="88" t="s">
+      <c r="C54" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="89" t="s">
+      <c r="D54" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="85" t="s">
+      <c r="E54" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="86"/>
-      <c r="G54" s="87"/>
-      <c r="H54" s="85" t="s">
+      <c r="F54" s="75"/>
+      <c r="G54" s="76"/>
+      <c r="H54" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="I54" s="86"/>
-      <c r="J54" s="87"/>
-      <c r="K54" s="85" t="s">
+      <c r="I54" s="75"/>
+      <c r="J54" s="76"/>
+      <c r="K54" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="86"/>
-      <c r="M54" s="87"/>
+      <c r="L54" s="75"/>
+      <c r="M54" s="76"/>
     </row>
     <row r="55" spans="2:16">
-      <c r="B55" s="88"/>
-      <c r="C55" s="88" t="s">
+      <c r="B55" s="72"/>
+      <c r="C55" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D55" s="89"/>
+      <c r="D55" s="73"/>
       <c r="E55" s="30" t="s">
         <v>47</v>
       </c>
@@ -101894,59 +101894,59 @@
       </c>
     </row>
     <row r="66" spans="2:13">
-      <c r="B66" s="78" t="s">
+      <c r="B66" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="79"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="81">
+      <c r="C66" s="78"/>
+      <c r="D66" s="79"/>
+      <c r="E66" s="80">
         <v>0.7</v>
       </c>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
-      <c r="H66" s="83">
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
+      <c r="H66" s="82">
         <v>0.7</v>
       </c>
-      <c r="I66" s="82"/>
-      <c r="J66" s="82"/>
-      <c r="K66" s="83">
+      <c r="I66" s="81"/>
+      <c r="J66" s="81"/>
+      <c r="K66" s="82">
         <v>0.7</v>
       </c>
-      <c r="L66" s="82"/>
-      <c r="M66" s="84"/>
+      <c r="L66" s="81"/>
+      <c r="M66" s="83"/>
     </row>
     <row r="68" spans="2:13">
-      <c r="B68" s="88" t="s">
+      <c r="B68" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C68" s="88" t="s">
+      <c r="C68" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D68" s="89" t="s">
+      <c r="D68" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E68" s="85" t="s">
+      <c r="E68" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F68" s="86"/>
-      <c r="G68" s="87"/>
-      <c r="H68" s="85" t="s">
+      <c r="F68" s="75"/>
+      <c r="G68" s="76"/>
+      <c r="H68" s="74" t="s">
         <v>45</v>
       </c>
-      <c r="I68" s="86"/>
-      <c r="J68" s="87"/>
-      <c r="K68" s="85" t="s">
+      <c r="I68" s="75"/>
+      <c r="J68" s="76"/>
+      <c r="K68" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="L68" s="86"/>
-      <c r="M68" s="87"/>
+      <c r="L68" s="75"/>
+      <c r="M68" s="76"/>
     </row>
     <row r="69" spans="2:13">
-      <c r="B69" s="88"/>
-      <c r="C69" s="88" t="s">
+      <c r="B69" s="72"/>
+      <c r="C69" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D69" s="89"/>
+      <c r="D69" s="73"/>
       <c r="E69" s="30" t="s">
         <v>47</v>
       </c>
@@ -102356,54 +102356,54 @@
       </c>
     </row>
     <row r="80" spans="2:13">
-      <c r="B80" s="78" t="s">
+      <c r="B80" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C80" s="79"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="81">
+      <c r="C80" s="78"/>
+      <c r="D80" s="79"/>
+      <c r="E80" s="80">
         <v>0.4</v>
       </c>
-      <c r="F80" s="82"/>
-      <c r="G80" s="82"/>
-      <c r="H80" s="83">
+      <c r="F80" s="81"/>
+      <c r="G80" s="81"/>
+      <c r="H80" s="82">
         <v>0.3</v>
       </c>
-      <c r="I80" s="82"/>
-      <c r="J80" s="82"/>
-      <c r="K80" s="83">
+      <c r="I80" s="81"/>
+      <c r="J80" s="81"/>
+      <c r="K80" s="82">
         <v>0.5</v>
       </c>
-      <c r="L80" s="82"/>
-      <c r="M80" s="84"/>
+      <c r="L80" s="81"/>
+      <c r="M80" s="83"/>
     </row>
     <row r="82" spans="2:13">
-      <c r="B82" s="88" t="s">
+      <c r="B82" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C82" s="88" t="s">
+      <c r="C82" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D82" s="89" t="s">
+      <c r="D82" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E82" s="85" t="s">
+      <c r="E82" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="86"/>
-      <c r="G82" s="86"/>
-      <c r="H82" s="90" t="s">
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="I82" s="86"/>
-      <c r="J82" s="91"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="85"/>
     </row>
     <row r="83" spans="2:13">
-      <c r="B83" s="88"/>
-      <c r="C83" s="88" t="s">
+      <c r="B83" s="72"/>
+      <c r="C83" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D83" s="89"/>
+      <c r="D83" s="73"/>
       <c r="E83" s="30" t="s">
         <v>47</v>
       </c>
@@ -102540,21 +102540,21 @@
       </c>
     </row>
     <row r="88" spans="2:13">
-      <c r="B88" s="78" t="s">
+      <c r="B88" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C88" s="79"/>
-      <c r="D88" s="80"/>
-      <c r="E88" s="81">
+      <c r="C88" s="78"/>
+      <c r="D88" s="79"/>
+      <c r="E88" s="80">
         <v>0.75</v>
       </c>
-      <c r="F88" s="82"/>
-      <c r="G88" s="82"/>
-      <c r="H88" s="83">
+      <c r="F88" s="81"/>
+      <c r="G88" s="81"/>
+      <c r="H88" s="82">
         <v>0.75</v>
       </c>
-      <c r="I88" s="82"/>
-      <c r="J88" s="84"/>
+      <c r="I88" s="81"/>
+      <c r="J88" s="83"/>
     </row>
     <row r="89" spans="2:13">
       <c r="B89" s="32" t="s">
@@ -102691,26 +102691,26 @@
       <c r="M92" s="18"/>
     </row>
     <row r="93" spans="2:13">
-      <c r="B93" s="78" t="s">
+      <c r="B93" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C93" s="79"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="81">
+      <c r="C93" s="78"/>
+      <c r="D93" s="79"/>
+      <c r="E93" s="80">
         <v>0.75</v>
       </c>
-      <c r="F93" s="82"/>
-      <c r="G93" s="82"/>
-      <c r="H93" s="83">
+      <c r="F93" s="81"/>
+      <c r="G93" s="81"/>
+      <c r="H93" s="82">
         <v>0.5</v>
       </c>
-      <c r="I93" s="82"/>
-      <c r="J93" s="84"/>
-      <c r="K93" s="83">
-        <v>0</v>
-      </c>
-      <c r="L93" s="82"/>
-      <c r="M93" s="84"/>
+      <c r="I93" s="81"/>
+      <c r="J93" s="83"/>
+      <c r="K93" s="82">
+        <v>0</v>
+      </c>
+      <c r="L93" s="81"/>
+      <c r="M93" s="83"/>
     </row>
     <row r="94" spans="2:13">
       <c r="B94" s="32" t="s">
@@ -102829,49 +102829,49 @@
       </c>
     </row>
     <row r="98" spans="2:10">
-      <c r="B98" s="78" t="s">
+      <c r="B98" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C98" s="79"/>
-      <c r="D98" s="80"/>
-      <c r="E98" s="81">
+      <c r="C98" s="78"/>
+      <c r="D98" s="79"/>
+      <c r="E98" s="80">
         <v>0.25</v>
       </c>
-      <c r="F98" s="82"/>
-      <c r="G98" s="82"/>
-      <c r="H98" s="83">
+      <c r="F98" s="81"/>
+      <c r="G98" s="81"/>
+      <c r="H98" s="82">
         <v>0.5</v>
       </c>
-      <c r="I98" s="82"/>
-      <c r="J98" s="84"/>
+      <c r="I98" s="81"/>
+      <c r="J98" s="83"/>
     </row>
     <row r="100" spans="2:10">
-      <c r="B100" s="88" t="s">
+      <c r="B100" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C100" s="88" t="s">
+      <c r="C100" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="89" t="s">
+      <c r="D100" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="E100" s="85" t="s">
+      <c r="E100" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="86"/>
-      <c r="G100" s="86"/>
-      <c r="H100" s="90" t="s">
+      <c r="F100" s="75"/>
+      <c r="G100" s="75"/>
+      <c r="H100" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="I100" s="86"/>
-      <c r="J100" s="91"/>
+      <c r="I100" s="75"/>
+      <c r="J100" s="85"/>
     </row>
     <row r="101" spans="2:10">
-      <c r="B101" s="88"/>
-      <c r="C101" s="88" t="s">
+      <c r="B101" s="72"/>
+      <c r="C101" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="D101" s="89"/>
+      <c r="D101" s="73"/>
       <c r="E101" s="30" t="s">
         <v>47</v>
       </c>
@@ -103008,21 +103008,21 @@
       </c>
     </row>
     <row r="106" spans="2:10">
-      <c r="B106" s="78" t="s">
+      <c r="B106" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C106" s="79"/>
-      <c r="D106" s="80"/>
-      <c r="E106" s="81">
+      <c r="C106" s="78"/>
+      <c r="D106" s="79"/>
+      <c r="E106" s="80">
         <v>0.5</v>
       </c>
-      <c r="F106" s="82"/>
-      <c r="G106" s="82"/>
-      <c r="H106" s="83">
+      <c r="F106" s="81"/>
+      <c r="G106" s="81"/>
+      <c r="H106" s="82">
         <v>0.75</v>
       </c>
-      <c r="I106" s="82"/>
-      <c r="J106" s="84"/>
+      <c r="I106" s="81"/>
+      <c r="J106" s="83"/>
     </row>
     <row r="107" spans="2:10">
       <c r="B107" s="32" t="s">
@@ -103141,21 +103141,21 @@
       </c>
     </row>
     <row r="111" spans="2:10">
-      <c r="B111" s="78" t="s">
+      <c r="B111" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C111" s="79"/>
-      <c r="D111" s="80"/>
-      <c r="E111" s="81">
+      <c r="C111" s="78"/>
+      <c r="D111" s="79"/>
+      <c r="E111" s="80">
         <v>0.25</v>
       </c>
-      <c r="F111" s="82"/>
-      <c r="G111" s="82"/>
-      <c r="H111" s="83">
+      <c r="F111" s="81"/>
+      <c r="G111" s="81"/>
+      <c r="H111" s="82">
         <v>0.75</v>
       </c>
-      <c r="I111" s="82"/>
-      <c r="J111" s="84"/>
+      <c r="I111" s="81"/>
+      <c r="J111" s="83"/>
     </row>
     <row r="112" spans="2:10">
       <c r="B112" s="32" t="s">
@@ -103274,21 +103274,21 @@
       </c>
     </row>
     <row r="116" spans="2:23">
-      <c r="B116" s="78" t="s">
+      <c r="B116" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C116" s="79"/>
-      <c r="D116" s="80"/>
-      <c r="E116" s="81">
+      <c r="C116" s="78"/>
+      <c r="D116" s="79"/>
+      <c r="E116" s="80">
         <v>0.25</v>
       </c>
-      <c r="F116" s="82"/>
-      <c r="G116" s="82"/>
-      <c r="H116" s="83">
+      <c r="F116" s="81"/>
+      <c r="G116" s="81"/>
+      <c r="H116" s="82">
         <v>0.5</v>
       </c>
-      <c r="I116" s="82"/>
-      <c r="J116" s="84"/>
+      <c r="I116" s="81"/>
+      <c r="J116" s="83"/>
     </row>
     <row r="121" spans="2:23">
       <c r="B121" s="62" t="s">
@@ -103300,21 +103300,21 @@
       <c r="D121" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="E121" s="85" t="s">
+      <c r="E121" s="74" t="s">
         <v>52</v>
       </c>
-      <c r="F121" s="86"/>
-      <c r="G121" s="87"/>
-      <c r="H121" s="85" t="s">
+      <c r="F121" s="75"/>
+      <c r="G121" s="76"/>
+      <c r="H121" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="I121" s="86"/>
-      <c r="J121" s="87"/>
-      <c r="K121" s="85" t="s">
+      <c r="I121" s="75"/>
+      <c r="J121" s="76"/>
+      <c r="K121" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="L121" s="86"/>
-      <c r="M121" s="87"/>
+      <c r="L121" s="75"/>
+      <c r="M121" s="76"/>
       <c r="R121" s="59" t="s">
         <v>4</v>
       </c>
@@ -103344,21 +103344,21 @@
       <c r="D122" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E122" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="73"/>
-      <c r="G122" s="74"/>
-      <c r="H122" s="72" t="s">
+      <c r="E122" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F122" s="87"/>
+      <c r="G122" s="88"/>
+      <c r="H122" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="I122" s="73"/>
-      <c r="J122" s="74"/>
-      <c r="K122" s="72" t="s">
+      <c r="I122" s="87"/>
+      <c r="J122" s="88"/>
+      <c r="K122" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="L122" s="73"/>
-      <c r="M122" s="74"/>
+      <c r="L122" s="87"/>
+      <c r="M122" s="88"/>
       <c r="R122" s="32" t="s">
         <v>11</v>
       </c>
@@ -103388,21 +103388,21 @@
       <c r="D123" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E123" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" s="76"/>
-      <c r="G123" s="77"/>
-      <c r="H123" s="75" t="s">
+      <c r="E123" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F123" s="90"/>
+      <c r="G123" s="91"/>
+      <c r="H123" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="I123" s="76"/>
-      <c r="J123" s="77"/>
-      <c r="K123" s="75" t="s">
+      <c r="I123" s="90"/>
+      <c r="J123" s="91"/>
+      <c r="K123" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="L123" s="76"/>
-      <c r="M123" s="77"/>
+      <c r="L123" s="90"/>
+      <c r="M123" s="91"/>
       <c r="R123" s="34" t="s">
         <v>22</v>
       </c>
@@ -103432,21 +103432,21 @@
       <c r="D124" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E124" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="73"/>
-      <c r="G124" s="74"/>
-      <c r="H124" s="72" t="s">
+      <c r="E124" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="87"/>
+      <c r="G124" s="88"/>
+      <c r="H124" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="I124" s="73"/>
-      <c r="J124" s="74"/>
-      <c r="K124" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="L124" s="73"/>
-      <c r="M124" s="74"/>
+      <c r="I124" s="87"/>
+      <c r="J124" s="88"/>
+      <c r="K124" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="L124" s="87"/>
+      <c r="M124" s="88"/>
       <c r="R124" s="35" t="s">
         <v>18</v>
       </c>
@@ -103476,21 +103476,21 @@
       <c r="D125" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E125" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="76"/>
-      <c r="G125" s="77"/>
-      <c r="H125" s="75" t="s">
+      <c r="E125" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" s="90"/>
+      <c r="G125" s="91"/>
+      <c r="H125" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="I125" s="76"/>
-      <c r="J125" s="77"/>
-      <c r="K125" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="L125" s="76"/>
-      <c r="M125" s="77"/>
+      <c r="I125" s="90"/>
+      <c r="J125" s="91"/>
+      <c r="K125" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="L125" s="90"/>
+      <c r="M125" s="91"/>
       <c r="R125" s="34" t="s">
         <v>23</v>
       </c>
@@ -103520,21 +103520,21 @@
       <c r="D126" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E126" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="73"/>
-      <c r="G126" s="74"/>
-      <c r="H126" s="72" t="s">
+      <c r="E126" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="87"/>
+      <c r="G126" s="88"/>
+      <c r="H126" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="I126" s="73"/>
-      <c r="J126" s="74"/>
-      <c r="K126" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="L126" s="73"/>
-      <c r="M126" s="74"/>
+      <c r="I126" s="87"/>
+      <c r="J126" s="88"/>
+      <c r="K126" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="L126" s="87"/>
+      <c r="M126" s="88"/>
       <c r="R126" s="35" t="s">
         <v>29</v>
       </c>
@@ -103564,21 +103564,21 @@
       <c r="D127" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E127" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="76"/>
-      <c r="G127" s="77"/>
-      <c r="H127" s="75" t="s">
+      <c r="E127" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="90"/>
+      <c r="G127" s="91"/>
+      <c r="H127" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="I127" s="76"/>
-      <c r="J127" s="77"/>
-      <c r="K127" s="75" t="s">
+      <c r="I127" s="90"/>
+      <c r="J127" s="91"/>
+      <c r="K127" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="L127" s="76"/>
-      <c r="M127" s="77"/>
+      <c r="L127" s="90"/>
+      <c r="M127" s="91"/>
       <c r="R127" s="34" t="s">
         <v>27</v>
       </c>
@@ -103608,21 +103608,21 @@
       <c r="D128" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E128" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" s="73"/>
-      <c r="G128" s="74"/>
-      <c r="H128" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="I128" s="73"/>
-      <c r="J128" s="74"/>
-      <c r="K128" s="72" t="s">
+      <c r="E128" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F128" s="87"/>
+      <c r="G128" s="88"/>
+      <c r="H128" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I128" s="87"/>
+      <c r="J128" s="88"/>
+      <c r="K128" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="L128" s="73"/>
-      <c r="M128" s="74"/>
+      <c r="L128" s="87"/>
+      <c r="M128" s="88"/>
       <c r="R128" s="35" t="s">
         <v>38</v>
       </c>
@@ -103652,21 +103652,21 @@
       <c r="D129" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E129" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129" s="76"/>
-      <c r="G129" s="77"/>
-      <c r="H129" s="75" t="s">
+      <c r="E129" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" s="90"/>
+      <c r="G129" s="91"/>
+      <c r="H129" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="I129" s="76"/>
-      <c r="J129" s="77"/>
-      <c r="K129" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="L129" s="76"/>
-      <c r="M129" s="77"/>
+      <c r="I129" s="90"/>
+      <c r="J129" s="91"/>
+      <c r="K129" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="L129" s="90"/>
+      <c r="M129" s="91"/>
       <c r="R129" s="34" t="s">
         <v>24</v>
       </c>
@@ -103696,21 +103696,21 @@
       <c r="D130" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E130" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F130" s="73"/>
-      <c r="G130" s="74"/>
-      <c r="H130" s="72" t="s">
+      <c r="E130" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="F130" s="87"/>
+      <c r="G130" s="88"/>
+      <c r="H130" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="I130" s="73"/>
-      <c r="J130" s="74"/>
-      <c r="K130" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="L130" s="73"/>
-      <c r="M130" s="74"/>
+      <c r="I130" s="87"/>
+      <c r="J130" s="88"/>
+      <c r="K130" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="L130" s="87"/>
+      <c r="M130" s="88"/>
       <c r="R130" s="36" t="s">
         <v>50</v>
       </c>
@@ -103740,21 +103740,21 @@
       <c r="D131" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="E131" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="76"/>
-      <c r="G131" s="77"/>
-      <c r="H131" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="I131" s="76"/>
-      <c r="J131" s="77"/>
-      <c r="K131" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="L131" s="76"/>
-      <c r="M131" s="77"/>
+      <c r="E131" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="90"/>
+      <c r="G131" s="91"/>
+      <c r="H131" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="I131" s="90"/>
+      <c r="J131" s="91"/>
+      <c r="K131" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="L131" s="90"/>
+      <c r="M131" s="91"/>
       <c r="R131" s="34" t="s">
         <v>19</v>
       </c>
@@ -103775,31 +103775,31 @@
       </c>
     </row>
     <row r="132" spans="2:23">
-      <c r="B132" s="78" t="s">
+      <c r="B132" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C132" s="79"/>
-      <c r="D132" s="80"/>
-      <c r="E132" s="81">
+      <c r="C132" s="78"/>
+      <c r="D132" s="79"/>
+      <c r="E132" s="80">
         <v>0.7</v>
       </c>
-      <c r="F132" s="82"/>
-      <c r="G132" s="82"/>
-      <c r="H132" s="83">
+      <c r="F132" s="81"/>
+      <c r="G132" s="81"/>
+      <c r="H132" s="82">
         <v>0.2</v>
       </c>
-      <c r="I132" s="82"/>
-      <c r="J132" s="82"/>
-      <c r="K132" s="83">
+      <c r="I132" s="81"/>
+      <c r="J132" s="81"/>
+      <c r="K132" s="82">
         <v>0.8</v>
       </c>
-      <c r="L132" s="82"/>
-      <c r="M132" s="84"/>
-      <c r="R132" s="78" t="s">
+      <c r="L132" s="81"/>
+      <c r="M132" s="83"/>
+      <c r="R132" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="S132" s="79"/>
-      <c r="T132" s="80"/>
+      <c r="S132" s="78"/>
+      <c r="T132" s="79"/>
       <c r="U132" s="57">
         <v>0.7</v>
       </c>
@@ -103812,6 +103812,103 @@
     </row>
   </sheetData>
   <mergeCells count="121">
+    <mergeCell ref="K122:M122"/>
+    <mergeCell ref="K123:M123"/>
+    <mergeCell ref="K124:M124"/>
+    <mergeCell ref="K125:M125"/>
+    <mergeCell ref="K126:M126"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="H130:J130"/>
+    <mergeCell ref="H131:J131"/>
+    <mergeCell ref="R132:T132"/>
+    <mergeCell ref="K127:M127"/>
+    <mergeCell ref="K128:M128"/>
+    <mergeCell ref="K129:M129"/>
+    <mergeCell ref="K130:M130"/>
+    <mergeCell ref="K131:M131"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="E132:G132"/>
+    <mergeCell ref="H132:J132"/>
+    <mergeCell ref="K132:M132"/>
+    <mergeCell ref="E121:G121"/>
+    <mergeCell ref="H121:J121"/>
+    <mergeCell ref="K121:M121"/>
+    <mergeCell ref="E122:G122"/>
+    <mergeCell ref="E123:G123"/>
+    <mergeCell ref="E124:G124"/>
+    <mergeCell ref="E125:G125"/>
+    <mergeCell ref="E126:G126"/>
+    <mergeCell ref="E127:G127"/>
+    <mergeCell ref="E128:G128"/>
+    <mergeCell ref="E129:G129"/>
+    <mergeCell ref="E130:G130"/>
+    <mergeCell ref="E131:G131"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="H123:J123"/>
+    <mergeCell ref="H124:J124"/>
+    <mergeCell ref="H125:J125"/>
+    <mergeCell ref="H126:J126"/>
+    <mergeCell ref="H127:J127"/>
+    <mergeCell ref="H128:J128"/>
+    <mergeCell ref="K93:M93"/>
+    <mergeCell ref="B111:D111"/>
+    <mergeCell ref="E111:G111"/>
+    <mergeCell ref="H111:J111"/>
+    <mergeCell ref="B106:D106"/>
+    <mergeCell ref="E106:G106"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="B98:D98"/>
+    <mergeCell ref="E98:G98"/>
+    <mergeCell ref="H98:J98"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E100:G100"/>
+    <mergeCell ref="H100:J100"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="E93:G93"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="E116:G116"/>
+    <mergeCell ref="H116:J116"/>
+    <mergeCell ref="E54:G54"/>
+    <mergeCell ref="H54:J54"/>
+    <mergeCell ref="K54:M54"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="H88:J88"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="D82:D83"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="K68:M68"/>
+    <mergeCell ref="B80:D80"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="K80:M80"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="K66:M66"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="E52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="K52:M52"/>
+    <mergeCell ref="N52:P52"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -103836,103 +103933,6 @@
     <mergeCell ref="K14:M14"/>
     <mergeCell ref="N14:P14"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="K68:M68"/>
-    <mergeCell ref="B80:D80"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="K80:M80"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="D68:D69"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="K66:M66"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="E52:G52"/>
-    <mergeCell ref="H52:J52"/>
-    <mergeCell ref="K52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="E54:G54"/>
-    <mergeCell ref="H54:J54"/>
-    <mergeCell ref="K54:M54"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="B88:D88"/>
-    <mergeCell ref="E88:G88"/>
-    <mergeCell ref="H88:J88"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="D82:D83"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="E100:G100"/>
-    <mergeCell ref="H100:J100"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="E93:G93"/>
-    <mergeCell ref="H93:J93"/>
-    <mergeCell ref="B116:D116"/>
-    <mergeCell ref="E116:G116"/>
-    <mergeCell ref="H116:J116"/>
-    <mergeCell ref="K93:M93"/>
-    <mergeCell ref="B111:D111"/>
-    <mergeCell ref="E111:G111"/>
-    <mergeCell ref="H111:J111"/>
-    <mergeCell ref="B106:D106"/>
-    <mergeCell ref="E106:G106"/>
-    <mergeCell ref="H106:J106"/>
-    <mergeCell ref="B98:D98"/>
-    <mergeCell ref="E98:G98"/>
-    <mergeCell ref="H98:J98"/>
-    <mergeCell ref="B132:D132"/>
-    <mergeCell ref="E132:G132"/>
-    <mergeCell ref="H132:J132"/>
-    <mergeCell ref="K132:M132"/>
-    <mergeCell ref="E121:G121"/>
-    <mergeCell ref="H121:J121"/>
-    <mergeCell ref="K121:M121"/>
-    <mergeCell ref="E122:G122"/>
-    <mergeCell ref="E123:G123"/>
-    <mergeCell ref="E124:G124"/>
-    <mergeCell ref="E125:G125"/>
-    <mergeCell ref="E126:G126"/>
-    <mergeCell ref="E127:G127"/>
-    <mergeCell ref="E128:G128"/>
-    <mergeCell ref="E129:G129"/>
-    <mergeCell ref="E130:G130"/>
-    <mergeCell ref="E131:G131"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="H123:J123"/>
-    <mergeCell ref="H124:J124"/>
-    <mergeCell ref="H125:J125"/>
-    <mergeCell ref="H126:J126"/>
-    <mergeCell ref="H127:J127"/>
-    <mergeCell ref="H128:J128"/>
-    <mergeCell ref="K122:M122"/>
-    <mergeCell ref="K123:M123"/>
-    <mergeCell ref="K124:M124"/>
-    <mergeCell ref="K125:M125"/>
-    <mergeCell ref="K126:M126"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="H130:J130"/>
-    <mergeCell ref="H131:J131"/>
-    <mergeCell ref="R132:T132"/>
-    <mergeCell ref="K127:M127"/>
-    <mergeCell ref="K128:M128"/>
-    <mergeCell ref="K129:M129"/>
-    <mergeCell ref="K130:M130"/>
-    <mergeCell ref="K131:M131"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
